--- a/Data/总结报表.xlsx
+++ b/Data/总结报表.xlsx
@@ -17,12 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="98">
   <si>
     <t>主管医生</t>
   </si>
   <si>
-    <t>49位医生办理日间手术</t>
+    <t>50位医生办理日间手术</t>
   </si>
   <si>
     <t>吴华荣</t>
@@ -31,12 +31,12 @@
     <t>王会旺</t>
   </si>
   <si>
+    <t>蔡金生</t>
+  </si>
+  <si>
     <t>徐伟坤</t>
   </si>
   <si>
-    <t>蔡金生</t>
-  </si>
-  <si>
     <t>张梦鑫</t>
   </si>
   <si>
@@ -49,21 +49,21 @@
     <t>张尚普</t>
   </si>
   <si>
+    <t>潘来辉</t>
+  </si>
+  <si>
     <t>白栩搏</t>
   </si>
   <si>
+    <t>张连锁</t>
+  </si>
+  <si>
     <t>陈子奇</t>
   </si>
   <si>
-    <t>潘来辉</t>
-  </si>
-  <si>
     <t>贾丁丁</t>
   </si>
   <si>
-    <t>张连锁</t>
-  </si>
-  <si>
     <t>刘阳</t>
   </si>
   <si>
@@ -76,66 +76,81 @@
     <t>宁胜华</t>
   </si>
   <si>
+    <t>张昕</t>
+  </si>
+  <si>
     <t>游小军</t>
   </si>
   <si>
-    <t>张昕</t>
+    <t>范会龙</t>
   </si>
   <si>
     <t>李琰</t>
   </si>
   <si>
-    <t>范会龙</t>
-  </si>
-  <si>
     <t>李继凯</t>
   </si>
   <si>
+    <t>王少锋</t>
+  </si>
+  <si>
     <t>郝运兵</t>
   </si>
   <si>
-    <t>王少锋</t>
-  </si>
-  <si>
     <t>白杰</t>
   </si>
   <si>
     <t>刘庆辉</t>
   </si>
   <si>
+    <t>程旭</t>
+  </si>
+  <si>
     <t>王学攀</t>
   </si>
   <si>
+    <t>赵书明</t>
+  </si>
+  <si>
     <t>郭二松</t>
   </si>
   <si>
     <t>张翼飞</t>
   </si>
   <si>
-    <t>赵书明</t>
+    <t>高文华</t>
+  </si>
+  <si>
+    <t>刘月星</t>
   </si>
   <si>
     <t>魏召劝</t>
   </si>
   <si>
+    <t>薛晓乐</t>
+  </si>
+  <si>
+    <t>刘玉波</t>
+  </si>
+  <si>
+    <t>刘林周</t>
+  </si>
+  <si>
     <t>李少青</t>
   </si>
   <si>
-    <t>刘月星</t>
-  </si>
-  <si>
-    <t>刘林周</t>
-  </si>
-  <si>
-    <t>薛晓乐</t>
-  </si>
-  <si>
-    <t>高文华</t>
+    <t>段智睿</t>
+  </si>
+  <si>
+    <t>高勇岗</t>
   </si>
   <si>
     <t>朱文博</t>
   </si>
   <si>
+    <t>赵鹏浩</t>
+  </si>
+  <si>
     <t>张辰阳</t>
   </si>
   <si>
@@ -145,31 +160,19 @@
     <t>王振辉</t>
   </si>
   <si>
-    <t>赵鹏浩</t>
-  </si>
-  <si>
-    <t>高勇岗</t>
+    <t>刘学亮</t>
   </si>
   <si>
     <t>程子文</t>
   </si>
   <si>
-    <t>刘学亮</t>
-  </si>
-  <si>
-    <t>段智睿</t>
-  </si>
-  <si>
-    <t>刘玉波</t>
-  </si>
-  <si>
     <t>王冬月</t>
   </si>
   <si>
     <t>申军国</t>
   </si>
   <si>
-    <t>程旭</t>
+    <t>还未办理</t>
   </si>
   <si>
     <t>医生总数</t>
@@ -202,31 +205,31 @@
     <t>骨一科</t>
   </si>
   <si>
+    <t>骨四科</t>
+  </si>
+  <si>
+    <t>骨三科</t>
+  </si>
+  <si>
     <t>骨二科</t>
   </si>
   <si>
-    <t>骨三科</t>
-  </si>
-  <si>
-    <t>骨四科</t>
-  </si>
-  <si>
     <t>骨五科</t>
   </si>
   <si>
+    <t>骨十科</t>
+  </si>
+  <si>
     <t>外一科</t>
   </si>
   <si>
     <t>骨八科</t>
   </si>
   <si>
-    <t>骨十科</t>
-  </si>
-  <si>
     <t>科室总数</t>
   </si>
   <si>
-    <t>71位医生办理预住院</t>
+    <t>72位医生办理预住院</t>
   </si>
   <si>
     <t>曹旭阳</t>
@@ -244,30 +247,33 @@
     <t>郎彦飞</t>
   </si>
   <si>
+    <t>赵玉龙</t>
+  </si>
+  <si>
     <t>左百军</t>
   </si>
   <si>
-    <t>赵玉龙</t>
+    <t>侯心昕</t>
   </si>
   <si>
     <t>王彦伟</t>
   </si>
   <si>
+    <t>李向科</t>
+  </si>
+  <si>
     <t>吕庆列</t>
   </si>
   <si>
-    <t>李向科</t>
-  </si>
-  <si>
     <t>李栋</t>
   </si>
   <si>
-    <t>侯心昕</t>
-  </si>
-  <si>
     <t>李德磊</t>
   </si>
   <si>
+    <t>何举仁</t>
+  </si>
+  <si>
     <t>范永强</t>
   </si>
   <si>
@@ -277,22 +283,22 @@
     <t>杨良栋</t>
   </si>
   <si>
-    <t>何举仁</t>
+    <t>陈国江</t>
+  </si>
+  <si>
+    <t>高少科</t>
+  </si>
+  <si>
+    <t>郭志刚</t>
   </si>
   <si>
     <t>李强</t>
   </si>
   <si>
-    <t>陈国江</t>
-  </si>
-  <si>
-    <t>高少科</t>
-  </si>
-  <si>
-    <t>郭志刚</t>
-  </si>
-  <si>
     <t>孙国栋</t>
+  </si>
+  <si>
+    <t>蓝悦辉</t>
   </si>
   <si>
     <t>16个科室办理预住院</t>
@@ -636,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -652,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -660,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -668,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -676,7 +682,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -684,7 +690,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -692,7 +698,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -700,7 +706,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -708,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -716,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -724,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -732,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -740,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -748,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -756,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -764,7 +770,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -772,7 +778,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -780,7 +786,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -788,7 +794,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -796,7 +802,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -804,7 +810,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -812,7 +818,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -820,7 +826,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -828,7 +834,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -836,7 +842,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -860,7 +866,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -868,7 +874,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -892,7 +898,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -900,7 +906,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -908,7 +914,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -916,7 +922,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -940,7 +946,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -948,7 +954,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -956,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -964,7 +970,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1044,7 +1050,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1052,7 +1058,15 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>817</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53">
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -1067,87 +1081,87 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2">
-        <v>365</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1155,15 +1169,15 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1171,7 +1185,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -1179,7 +1193,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>13</v>
@@ -1187,10 +1201,10 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16">
-        <v>817</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -1200,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1208,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1216,23 +1230,23 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1240,116 +1254,116 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8">
         <v>71</v>
-      </c>
-      <c r="B8">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="B10">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B18">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>34</v>
@@ -1357,39 +1371,39 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B20">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B24">
         <v>30</v>
@@ -1397,74 +1411,74 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B31">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1472,12 +1486,12 @@
         <v>29</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>8</v>
@@ -1485,31 +1499,31 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -1517,7 +1531,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B40">
         <v>7</v>
@@ -1525,63 +1539,63 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -1589,7 +1603,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -1597,31 +1611,31 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1629,7 +1643,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -1637,10 +1651,10 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1648,7 +1662,7 @@
         <v>83</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1656,12 +1670,12 @@
         <v>84</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -1669,7 +1683,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -1677,7 +1691,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -1685,7 +1699,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -1693,7 +1707,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -1709,7 +1723,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -1717,7 +1731,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -1725,7 +1739,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -1733,7 +1747,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -1741,7 +1755,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1757,7 +1771,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -1765,7 +1779,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1781,10 +1795,10 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="B73">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1792,7 +1806,15 @@
         <v>52</v>
       </c>
       <c r="B74">
-        <v>1610</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>53</v>
+      </c>
+      <c r="B75">
+        <v>1762</v>
       </c>
     </row>
   </sheetData>
@@ -1807,103 +1829,103 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B2">
-        <v>469</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3">
-        <v>401</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4">
-        <v>372</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1911,15 +1933,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -1927,7 +1949,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -1935,7 +1957,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1943,7 +1965,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18">
         <v>16</v>
@@ -1951,10 +1973,10 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19">
-        <v>1610</v>
+        <v>1762</v>
       </c>
     </row>
   </sheetData>
